--- a/fixtures/acfc_shapes/sttm/pair_4_family_d.xlsx
+++ b/fixtures/acfc_shapes/sttm/pair_4_family_d.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1949,6 +1949,222 @@
       <c r="Y17" t="inlineStr">
         <is>
           <t>String</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Audit column</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>syn_dlk</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>stg_remit</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>feed_4_remit</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>SRC_FILE_NAME</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>syn_std</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>remit</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>feed_4_remit</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>SRC_FILE_NAME</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Audit column</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>syn_dlk</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>stg_remit</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>feed_4_remit</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>REC_CREATION_TIME</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>syn_std</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>remit</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>feed_4_remit</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>REC_CREATION_TIME</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Audit column</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>syn_dlk</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>stg_remit</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>feed_4_remit</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>REC_UPDATED_TIME</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>syn_std</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>remit</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>feed_4_remit</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>REC_UPDATED_TIME</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
         </is>
       </c>
     </row>
